--- a/r4-core-add-vbpk/ValueSet-at-core-valueset-vbpk.xlsx
+++ b/r4-core-add-vbpk/ValueSet-at-core-valueset-vbpk.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T11:03:52+00:00</t>
+    <t>2026-06-12T11:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,19 +102,19 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>1.2.40.0.34.4.22.1</t>
+    <t>urn:oid:1.2.40.0.34.4.22.1</t>
   </si>
   <si>
     <t>vbPK-GH</t>
   </si>
   <si>
-    <t>1.2.40.0.34.4.22.2</t>
+    <t>urn:oid:1.2.40.0.34.4.22.2</t>
   </si>
   <si>
     <t>vbPK-SV</t>
   </si>
   <si>
-    <t>1.2.40.0.34.4.22.3</t>
+    <t>urn:oid:1.2.40.0.34.4.22.3</t>
   </si>
   <si>
     <t>vbPK-AS</t>
@@ -123,7 +123,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:oid</t>
+    <t>urn:ietf:rfc:3986</t>
   </si>
 </sst>
 </file>
